--- a/evaluation_forms/047_new_year_039_s_marketing_campaign_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/047_new_year_039_s_marketing_campaign_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'success'}</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Success'}</t>
+          <t>Success</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'failure'}</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Failure'}</t>
+          <t>Failure</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'television'}</t>
+          <t>television</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Television'}</t>
+          <t>Television</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'survey'}</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Survey'}</t>
+          <t>Survey</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'focus_group'}</t>
+          <t>focus_group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Focus Group'}</t>
+          <t>Focus Group</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'poll'}</t>
+          <t>poll</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Poll'}</t>
+          <t>Poll</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'review'}</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Review'}</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
